--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.93326682645333</v>
+        <v>8.114155859298666</v>
       </c>
       <c r="D2" t="n">
-        <v>49.7487375124358</v>
+        <v>8.084169845770816</v>
       </c>
       <c r="E2" t="n">
-        <v>19.35716046246144</v>
+        <v>3.145538575149983</v>
       </c>
       <c r="F2" t="n">
-        <v>19.35663484778731</v>
+        <v>3.145453162765438</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.64618078890067</v>
+        <v>8.067504378196359</v>
       </c>
       <c r="D3" t="n">
-        <v>49.52188471274322</v>
+        <v>8.047306265820772</v>
       </c>
       <c r="E3" t="n">
-        <v>19.35716046246144</v>
+        <v>3.145538575149983</v>
       </c>
       <c r="F3" t="n">
-        <v>19.35663484778731</v>
+        <v>3.145453162765438</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.35921313788249</v>
+        <v>7.370872134905905</v>
       </c>
       <c r="D4" t="n">
-        <v>45.35370417608697</v>
+        <v>7.369976928614133</v>
       </c>
       <c r="E4" t="n">
-        <v>19.35716046246144</v>
+        <v>3.145538575149983</v>
       </c>
       <c r="F4" t="n">
-        <v>19.35663484778731</v>
+        <v>3.145453162765438</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.805641780432299</v>
+        <v>0.6184167893202486</v>
       </c>
       <c r="D5" t="n">
-        <v>3.688898253561145</v>
+        <v>0.5994459662036862</v>
       </c>
       <c r="E5" t="n">
-        <v>19.35716046246144</v>
+        <v>3.145538575149983</v>
       </c>
       <c r="F5" t="n">
-        <v>19.35663484778731</v>
+        <v>3.145453162765438</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
